--- a/output/full_scan/batch_seq1_2026-10-21.xlsx
+++ b/output/full_scan/batch_seq1_2026-10-21.xlsx
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>206.5261175014786</v>
+        <v>206.5261175014785</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>42.1</v>
